--- a/dataset_thyroid.xlsx
+++ b/dataset_thyroid.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB9"/>
+  <dimension ref="A1:AB13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,6 +1255,358 @@
         <v>0</v>
       </c>
       <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>gyege</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>100</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sbhbdsh</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>100</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P-Disorder</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>40</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>100</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P-Healthy</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>40</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>100</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>100</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
         <v>0</v>
       </c>
     </row>
